--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.76689</v>
+        <v>17.88123</v>
       </c>
       <c r="D2" t="n">
-        <v>17.76984</v>
+        <v>17.40335</v>
       </c>
       <c r="E2" t="n">
-        <v>17.70762</v>
+        <v>17.4855</v>
       </c>
       <c r="F2" t="n">
-        <v>45.09554</v>
+        <v>45.11802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0529</v>
+        <v>0.05307</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94449</v>
+        <v>1.91164</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.72737</v>
+        <v>18.00998</v>
       </c>
       <c r="D3" t="n">
-        <v>17.8287</v>
+        <v>17.52503</v>
       </c>
       <c r="E3" t="n">
-        <v>17.91198</v>
+        <v>17.8065</v>
       </c>
       <c r="F3" t="n">
-        <v>45.10657</v>
+        <v>45.14936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05301</v>
+        <v>0.05508</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94689</v>
+        <v>1.91097</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.11114</v>
+        <v>18.14375</v>
       </c>
       <c r="D4" t="n">
-        <v>17.70746</v>
+        <v>17.63855</v>
       </c>
       <c r="E4" t="n">
-        <v>17.59347</v>
+        <v>17.87601</v>
       </c>
       <c r="F4" t="n">
-        <v>44.7288</v>
+        <v>44.93602</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05301</v>
+        <v>0.05457</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90473</v>
+        <v>1.94157</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.81106</v>
+        <v>17.38762</v>
       </c>
       <c r="D6" t="n">
-        <v>16.72558</v>
+        <v>16.63818</v>
       </c>
       <c r="E6" t="n">
-        <v>17.3936</v>
+        <v>17.16477</v>
       </c>
       <c r="F6" t="n">
-        <v>23.27343</v>
+        <v>22.98442</v>
       </c>
       <c r="G6" t="n">
-        <v>35.88415</v>
+        <v>36.49502</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.67368</v>
+        <v>17.68394</v>
       </c>
       <c r="D7" t="n">
-        <v>16.99271</v>
+        <v>16.8811</v>
       </c>
       <c r="E7" t="n">
-        <v>17.73012</v>
+        <v>17.64064</v>
       </c>
       <c r="F7" t="n">
-        <v>23.37712</v>
+        <v>22.88656</v>
       </c>
       <c r="G7" t="n">
-        <v>36.60663</v>
+        <v>35.81552</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.87683</v>
+        <v>17.75878</v>
       </c>
       <c r="D8" t="n">
-        <v>16.65387</v>
+        <v>16.93895</v>
       </c>
       <c r="E8" t="n">
-        <v>16.78273</v>
+        <v>17.09191</v>
       </c>
       <c r="F8" t="n">
-        <v>23.21804</v>
+        <v>23.17803</v>
       </c>
       <c r="G8" t="n">
-        <v>36.5899</v>
+        <v>34.94059</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.642</v>
+        <v>0.63624</v>
       </c>
       <c r="D10" t="n">
-        <v>1.20985</v>
+        <v>1.16912</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.65262</v>
+        <v>0.63675</v>
       </c>
       <c r="D11" t="n">
-        <v>1.19769</v>
+        <v>1.16554</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6531400000000001</v>
+        <v>0.63976</v>
       </c>
       <c r="D12" t="n">
-        <v>1.18015</v>
+        <v>1.16719</v>
       </c>
     </row>
   </sheetData>
